--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>82.67953983307177</v>
+        <v>13.43542522287416</v>
       </c>
       <c r="D2" t="n">
-        <v>61.50090333573249</v>
+        <v>9.99389679205653</v>
       </c>
       <c r="E2" t="n">
-        <v>23.13387312209201</v>
+        <v>3.759254382339952</v>
       </c>
       <c r="F2" t="n">
-        <v>22.19265891297528</v>
+        <v>3.606307073358484</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.0520929972554</v>
+        <v>3.908465112054002</v>
       </c>
       <c r="D3" t="n">
-        <v>3.556299001955695</v>
+        <v>0.5778985878178005</v>
       </c>
       <c r="E3" t="n">
-        <v>23.13387312209201</v>
+        <v>3.759254382339952</v>
       </c>
       <c r="F3" t="n">
-        <v>22.19265891297528</v>
+        <v>3.606307073358484</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.12689484434675</v>
+        <v>7.820620412206347</v>
       </c>
       <c r="D4" t="n">
-        <v>33.60431519909311</v>
+        <v>5.460701219852631</v>
       </c>
       <c r="E4" t="n">
-        <v>23.13387312209201</v>
+        <v>3.759254382339952</v>
       </c>
       <c r="F4" t="n">
-        <v>22.19265891297528</v>
+        <v>3.606307073358484</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.00136866748459</v>
+        <v>5.687722408466247</v>
       </c>
       <c r="D5" t="n">
-        <v>35.07611490014939</v>
+        <v>5.699868671274277</v>
       </c>
       <c r="E5" t="n">
-        <v>23.13387312209201</v>
+        <v>3.759254382339952</v>
       </c>
       <c r="F5" t="n">
-        <v>22.19265891297528</v>
+        <v>3.606307073358484</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.37882853820629</v>
+        <v>1.036559637458522</v>
       </c>
       <c r="D6" t="n">
-        <v>6.455712094212696</v>
+        <v>1.049053215309563</v>
       </c>
       <c r="E6" t="n">
-        <v>23.13387312209201</v>
+        <v>3.759254382339952</v>
       </c>
       <c r="F6" t="n">
-        <v>22.19265891297528</v>
+        <v>3.606307073358484</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>60.61286856893108</v>
+        <v>9.849591142451301</v>
       </c>
       <c r="D7" t="n">
-        <v>60.59858872298594</v>
+        <v>9.847270667485216</v>
       </c>
       <c r="E7" t="n">
-        <v>23.13387312209201</v>
+        <v>3.759254382339952</v>
       </c>
       <c r="F7" t="n">
-        <v>22.19265891297528</v>
+        <v>3.606307073358484</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>61.94677266682031</v>
+        <v>10.0663505583583</v>
       </c>
       <c r="D8" t="n">
-        <v>62.08528489176395</v>
+        <v>10.08885879491164</v>
       </c>
       <c r="E8" t="n">
-        <v>23.13387312209201</v>
+        <v>3.759254382339952</v>
       </c>
       <c r="F8" t="n">
-        <v>22.19265891297528</v>
+        <v>3.606307073358484</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.25578271479734</v>
+        <v>4.429064691154568</v>
       </c>
       <c r="D9" t="n">
-        <v>27.46091584522679</v>
+        <v>4.462398824849354</v>
       </c>
       <c r="E9" t="n">
-        <v>23.13387312209201</v>
+        <v>3.759254382339952</v>
       </c>
       <c r="F9" t="n">
-        <v>22.19265891297528</v>
+        <v>3.606307073358484</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
